--- a/templates/dennis_data_template.xlsx
+++ b/templates/dennis_data_template.xlsx
@@ -162,7 +162,7 @@
     <t>ticker</t>
   </si>
   <si>
-    <t>Ticker / RIC</t>
+    <t>Ticker</t>
   </si>
   <si>
     <t>exchange</t>
@@ -3446,8 +3446,8 @@
         <v>25</v>
       </c>
       <c r="D8" s="10" t="str">
-        <f>$B$3</f>
-        <v>meta.O</v>
+        <f>$C$3</f>
+        <v>meta</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="8" t="s">

--- a/templates/dennis_data_template.xlsx
+++ b/templates/dennis_data_template.xlsx
@@ -9,13 +9,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_CIQHiddenCacheSheet" sheetId="1" state="veryHidden" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshot" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZDdiODliMGYtNjhhNC00OT" sheetId="5" state="veryHidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peers" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_RICMap" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarters" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZDdiODliMGYtNjhhNC00OT" sheetId="6" state="veryHidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_RICMap" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="CIQWBGuid" hidden="1">"070e9992-7c22-4f2c-8d24-f1b9c95e8af0"</definedName>
@@ -1257,6 +1258,172 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="116" customWidth="1" style="90" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1" s="90">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>DENNIS — data template v3 (automated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="36" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="37" t="inlineStr">
+        <is>
+          <t>What changed: the add-in TR formulas are PRE-FILLED. You just set the ticker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Set the RIC in Snapshot!B2. Every green cell auto-pulls; grey cells auto-calc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Make sure the LSEG/Refinitiv Excel add-in is loaded, then refresh ( / recalc ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Verify the mnemonics in the last column against your entitlement — swap any that error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Save as data.xlsx into the video workspace ( workspace/&lt;TICKER&gt;/&lt;date&gt;/ ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>Peers auto-pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  The Peers sheet uses =TR("PEERS(&lt;ric&gt;)",...) to fetch Refinitiv's own peer list — no manual RICs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Peers is optional and mainly for long-form; skip it for daily shorts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cells show #NAME? until the add-in is loaded (the TR function) — that's expected, not a broken file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  % in POINTS. Currency absolute. Don't rename field_key rows. Bot reads sheets by name, periods dynamically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  On-screen the videos never name the data vendor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>What's new (v3.1 — automation upgrades)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RIC auto-suffix: Snapshot!B3 now derives the Refinitiv RIC from the Capital IQ exchange (D9) via the hidden _RICMap table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Set Snapshot!E2 to force a specific RIC. Default suffix .O if the exchange isn't recognised; edit _RICMap to add exchanges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Peers self-scoring: the Peers sheet now has a percentile block (PERCENTRANK.INC) — this ticker's rank vs peers per metric, with a cheap/expensive &amp; strong/weak read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Valuation: WACC (CAPM, auto) + a reverse DCF (implied growth = WACC − FCF/EV) vs historical CAGR. Bear/base/bull multiples auto-suggest from peer P/E percentiles (override anytime).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  News sheet: Capital IQ Key Developments (dated headlines) for the ticker — feeds headline-driven shorts. Verify IQ_KEY_DEV_* / IQ_NEWS mnemonics against your entitlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Quarters sheet: the last 8 reported quarters (IQ_FQ − 7 … IQ_FQ). The bot reads QoQ (vs Q-1) and YoY (vs Q-4) from it and prints BOTH — a seasonal Q4 beats its own Q3 every year, so one number alone is misleading. Optional: without it the annual flow is unchanged.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4610,6 +4777,1026 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="90" min="1" max="1"/>
+    <col width="22" customWidth="1" style="90" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DENNIS — quarterly results (8 quarters) + both comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Green rows auto-pull per quarter; grey rows auto-calc. Q-0 is the latest reported quarter. Read QoQ (Q-1) and YoY (Q-4) together — a retailer beats its own Q3 every December.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="93" t="inlineStr">
+        <is>
+          <t>field_key</t>
+        </is>
+      </c>
+      <c r="B4" s="93" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C4" s="93" t="inlineStr">
+        <is>
+          <t>Q-7</t>
+        </is>
+      </c>
+      <c r="D4" s="93" t="inlineStr">
+        <is>
+          <t>Q-6</t>
+        </is>
+      </c>
+      <c r="E4" s="93" t="inlineStr">
+        <is>
+          <t>Q-5</t>
+        </is>
+      </c>
+      <c r="F4" s="93" t="inlineStr">
+        <is>
+          <t>Q-4</t>
+        </is>
+      </c>
+      <c r="G4" s="93" t="inlineStr">
+        <is>
+          <t>Q-3</t>
+        </is>
+      </c>
+      <c r="H4" s="93" t="inlineStr">
+        <is>
+          <t>Q-2</t>
+        </is>
+      </c>
+      <c r="I4" s="93" t="inlineStr">
+        <is>
+          <t>Q-1</t>
+        </is>
+      </c>
+      <c r="J4" s="93" t="inlineStr">
+        <is>
+          <t>Q-0</t>
+        </is>
+      </c>
+      <c r="K4" s="93" t="inlineStr">
+        <is>
+          <t>Field mnemonic (verify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_REV", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_REV", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_REV", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_REV", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_REV", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_REV", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_REV", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_REV", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>TR.Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gross_profit</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_GP", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_GP", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_GP", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_GP", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_GP", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_GP", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_GP", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_GP", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>TR.GrossProfit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>IFERROR(C6/C5*100,"")</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>IFERROR(D6/D5*100,"")</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>IFERROR(E6/E5*100,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>IFERROR(F6/F5*100,"")</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IFERROR(G6/G5*100,"")</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>IFERROR(H6/H5*100,"")</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IFERROR(I6/I5*100,"")</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>IFERROR(J6/J5*100,"")</f>
+        <v/>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>operating_income</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_OPER_INC", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_OPER_INC", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_OPER_INC", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_OPER_INC", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_OPER_INC", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_OPER_INC", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_OPER_INC", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_OPER_INC", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>TR.OperatingIncome</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>operating_margin</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operating Margin %</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>IFERROR(C8/C5*100,"")</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>IFERROR(D8/D5*100,"")</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>IFERROR(E8/E5*100,"")</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>IFERROR(F8/F5*100,"")</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>IFERROR(G8/G5*100,"")</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>IFERROR(H8/H5*100,"")</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IFERROR(I8/I5*100,"")</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>IFERROR(J8/J5*100,"")</f>
+        <v/>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EBITDA", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EBITDA", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EBITDA", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EBITDA", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EBITDA", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EBITDA", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EBITDA", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_EBITDA", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>TR.EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_NI", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_NI", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_NI", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_NI", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_NI", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_NI", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_NI", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_NI", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TR.NetIncomeAfterTax</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>net_margin</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Net Margin %</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>IFERROR(C11/C5*100,"")</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>IFERROR(D11/D5*100,"")</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>IFERROR(E11/E5*100,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>IFERROR(F11/F5*100,"")</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>IFERROR(G11/G5*100,"")</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>IFERROR(H11/H5*100,"")</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IFERROR(I11/I5*100,"")</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>IFERROR(J11/J5*100,"")</f>
+        <v/>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>operating_cf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_OPER_CS", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_OPER_CS", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_OPER_CS", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_OPER_CS", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_OPER_CS", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_OPER_CS", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_OPER_CS", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_OPER_CS", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>TR.CashFromOperatingAct</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CAPEX", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CAPEX", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CAPEX", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CAPEX", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CAPEX", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CAPEX", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CAPEX", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J14">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CAPEX", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>TR.CapitalExpenditures</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fcf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>IF(C13="","",C13+C14)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>IF(D13="","",D13+D14)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>IF(E13="","",E13+E14)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>IF(F13="","",F13+F14)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>IF(G13="","",G13+G14)</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>IF(H13="","",H13+H14)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(I13="","",I13+I14)</f>
+        <v/>
+      </c>
+      <c r="J15">
+        <f>IF(J13="","",J13+J14)</f>
+        <v/>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fcf_margin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FCF Margin %</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>IFERROR(C15/C5*100,"")</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>IFERROR(D15/D5*100,"")</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>IFERROR(E15/E5*100,"")</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>IFERROR(F15/F5*100,"")</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>IFERROR(G15/G5*100,"")</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>IFERROR(H15/H5*100,"")</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IFERROR(I15/I5*100,"")</f>
+        <v/>
+      </c>
+      <c r="J16">
+        <f>IFERROR(J15/J5*100,"")</f>
+        <v/>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sbc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stock-Based Comp</t>
+        </is>
+      </c>
+      <c r="C17">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_STOCK_BASED_CF", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_STOCK_BASED_CF", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_STOCK_BASED_CF", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_STOCK_BASED_CF", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_STOCK_BASED_CF", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_STOCK_BASED_CF", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_STOCK_BASED_CF", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J17">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_STOCK_BASED_CF", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>TR.StockBasedCompensation</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cash &amp; Equivalents</t>
+        </is>
+      </c>
+      <c r="C18">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_ST_INVEST", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_ST_INVEST", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_ST_INVEST", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_ST_INVEST", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_ST_INVEST", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_ST_INVEST", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_ST_INVEST", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J18">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_CASH_ST_INVEST", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>TR.CashAndSTInvestments</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total_debt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_DEBT", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_DEBT", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_DEBT", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_DEBT", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_DEBT", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_DEBT", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_DEBT", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J19">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_DEBT", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>TR.TotalDebtOutstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>net_debt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>IF(C18="","",C18-C17)</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>IF(D18="","",D18-D17)</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>IF(E18="","",E18-E17)</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>IF(F18="","",F18-F17)</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>IF(G18="","",G18-G17)</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>IF(H18="","",H18-H17)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(I18="","",I18-I17)</f>
+        <v/>
+      </c>
+      <c r="J20">
+        <f>IF(J18="","",J18-J17)</f>
+        <v/>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>total_equity</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="C21">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_EQUITY", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_EQUITY", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_EQUITY", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_EQUITY", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_EQUITY", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_EQUITY", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_EQUITY", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J21">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_TOTAL_EQUITY", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>TR.TotalEquity</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>diluted_shares</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Diluted Shares</t>
+        </is>
+      </c>
+      <c r="C22">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_DILUT_WEIGHT", IQ_FQ - 7)</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_DILUT_WEIGHT", IQ_FQ - 6)</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_DILUT_WEIGHT", IQ_FQ - 5)</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_DILUT_WEIGHT", IQ_FQ - 4)</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_DILUT_WEIGHT", IQ_FQ - 3)</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_DILUT_WEIGHT", IQ_FQ - 2)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_DILUT_WEIGHT", IQ_FQ - 1)</f>
+        <v/>
+      </c>
+      <c r="J22">
+        <f>_xll.ciqfunctions.udf.CIQ(Snapshot!C3, "IQ_DILUT_WEIGHT", IQ_FQ)</f>
+        <v/>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>TR.DilutedWeightedAvgShares</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EPS (diluted)</t>
+        </is>
+      </c>
+      <c r="C23">
+        <f>IFERROR(C11/C22*1,"")</f>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>IFERROR(D11/D22*1,"")</f>
+        <v/>
+      </c>
+      <c r="E23">
+        <f>IFERROR(E11/E22*1,"")</f>
+        <v/>
+      </c>
+      <c r="F23">
+        <f>IFERROR(F11/F22*1,"")</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>IFERROR(G11/G22*1,"")</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>IFERROR(H11/H22*1,"")</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IFERROR(I11/I22*1,"")</f>
+        <v/>
+      </c>
+      <c r="J23">
+        <f>IFERROR(J11/J22*1,"")</f>
+        <v/>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5093,7 +6280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5106,7 +6293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10707,7 +11894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10992,7 +12179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11283,163 +12470,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="116" customWidth="1" style="90" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1" s="90">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>DENNIS — data template v3 (automated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="36" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="37" t="inlineStr">
-        <is>
-          <t>What changed: the add-in TR formulas are PRE-FILLED. You just set the ticker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Set the RIC in Snapshot!B2. Every green cell auto-pulls; grey cells auto-calc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Make sure the LSEG/Refinitiv Excel add-in is loaded, then refresh ( / recalc ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Verify the mnemonics in the last column against your entitlement — swap any that error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. Save as data.xlsx into the video workspace ( workspace/&lt;TICKER&gt;/&lt;date&gt;/ ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="37" t="inlineStr">
-        <is>
-          <t>Peers auto-pull</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  The Peers sheet uses =TR("PEERS(&lt;ric&gt;)",...) to fetch Refinitiv's own peer list — no manual RICs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Peers is optional and mainly for long-form; skip it for daily shorts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="37" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cells show #NAME? until the add-in is loaded (the TR function) — that's expected, not a broken file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  % in POINTS. Currency absolute. Don't rename field_key rows. Bot reads sheets by name, periods dynamically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  On-screen the videos never name the data vendor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>What's new (v3.1 — automation upgrades)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  RIC auto-suffix: Snapshot!B3 now derives the Refinitiv RIC from the Capital IQ exchange (D9) via the hidden _RICMap table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Set Snapshot!E2 to force a specific RIC. Default suffix .O if the exchange isn't recognised; edit _RICMap to add exchanges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Peers self-scoring: the Peers sheet now has a percentile block (PERCENTRANK.INC) — this ticker's rank vs peers per metric, with a cheap/expensive &amp; strong/weak read.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Valuation: WACC (CAPM, auto) + a reverse DCF (implied growth = WACC − FCF/EV) vs historical CAGR. Bear/base/bull multiples auto-suggest from peer P/E percentiles (override anytime).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  News sheet: Capital IQ Key Developments (dated headlines) for the ticker — feeds headline-driven shorts. Verify IQ_KEY_DEV_* / IQ_NEWS mnemonics against your entitlement.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>